--- a/01-digitaidot-ja-tiedostonhallinta/kirja/excel esimerkit.xlsx
+++ b/01-digitaidot-ja-tiedostonhallinta/kirja/excel esimerkit.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="64" documentId="8_{D270662D-75E8-4496-BFF5-EB71A791891B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F063576D-25C5-4C05-8A0D-47DCB7D378B4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{510FD49B-76B6-47FB-9915-215790234389}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="3150" windowWidth="11385" windowHeight="9360" activeTab="1" xr2:uid="{510FD49B-76B6-47FB-9915-215790234389}"/>
   </bookViews>
   <sheets>
     <sheet name="Täyttökahva" sheetId="2" r:id="rId1"/>

--- a/01-digitaidot-ja-tiedostonhallinta/kirja/excel esimerkit.xlsx
+++ b/01-digitaidot-ja-tiedostonhallinta/kirja/excel esimerkit.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="64" documentId="8_{D270662D-75E8-4496-BFF5-EB71A791891B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F063576D-25C5-4C05-8A0D-47DCB7D378B4}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="3150" windowWidth="11385" windowHeight="9360" activeTab="1" xr2:uid="{510FD49B-76B6-47FB-9915-215790234389}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{510FD49B-76B6-47FB-9915-215790234389}"/>
   </bookViews>
   <sheets>
     <sheet name="Täyttökahva" sheetId="2" r:id="rId1"/>
